--- a/FeFET_retention/1100_dac_retention_v2_20260719_171455.xlsx
+++ b/FeFET_retention/1100_dac_retention_v2_20260719_171455.xlsx
@@ -10,7 +10,7 @@
     <sheet name="sweeps" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="matrix_code" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="matrix_I_uA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="matrix_I_uA_nominal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="config" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -517,12 +517,12 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>I_A</t>
+          <t>I_A_nominal</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>I_uA</t>
+          <t>I_uA_nominal</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
